--- a/data/07_QUARTERLY_WEIGHTING/2024/T4/312X_1D/LFS_SAMPLE_DATA_2024_T4_312X_1D_SUMMARY_OF_Xs_SAMPLE_SIZE.xlsx
+++ b/data/07_QUARTERLY_WEIGHTING/2024/T4/312X_1D/LFS_SAMPLE_DATA_2024_T4_312X_1D_SUMMARY_OF_Xs_SAMPLE_SIZE.xlsx
@@ -1928,196 +1928,196 @@
         </is>
       </c>
       <c r="B2">
-        <v>1998</v>
+        <v>2005</v>
       </c>
       <c r="C2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="D2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E2">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="F2">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="G2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H2">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="I2">
         <v>191</v>
       </c>
       <c r="J2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="K2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="L2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M2">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="N2">
-        <v>2720</v>
+        <v>2728</v>
       </c>
       <c r="O2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="P2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="Q2">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="R2">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="S2">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="T2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="U2">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="V2">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="W2">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="X2">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="Y2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="Z2">
-        <v>2017</v>
+        <v>2026</v>
       </c>
       <c r="AA2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="AB2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="AC2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AD2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="AE2">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="AF2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="AG2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AH2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AI2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AJ2">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="AK2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AL2">
-        <v>2529</v>
+        <v>2535</v>
       </c>
       <c r="AM2">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="AN2">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="AO2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="AP2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AQ2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="AR2">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="AS2">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="AT2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AU2">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="AV2">
         <v>99</v>
       </c>
       <c r="AW2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AX2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AY2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AZ2">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="BA2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="BB2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="BC2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="BD2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="BE2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="BF2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BG2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="BH2">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="BI2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="BJ2">
         <v>83</v>
       </c>
       <c r="BK2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="BL2">
         <v>91</v>
       </c>
       <c r="BM2">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="BN2">
         <v>59</v>
@@ -2132,10 +2132,10 @@
         <v>95</v>
       </c>
       <c r="BR2">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BS2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="BT2">
         <v>71</v>
@@ -2150,10 +2150,10 @@
         <v>101</v>
       </c>
       <c r="BX2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="BY2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="BZ2">
         <v>30</v>
@@ -2162,10 +2162,10 @@
         <v>43</v>
       </c>
       <c r="CB2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="CC2">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="CD2">
         <v>63</v>
@@ -2192,16 +2192,16 @@
         <v>96</v>
       </c>
       <c r="CL2">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="CM2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="CN2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="CO2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="CP2">
         <v>79</v>
@@ -2216,10 +2216,10 @@
         <v>104</v>
       </c>
       <c r="CT2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="CU2">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="CV2">
         <v>46</v>
@@ -2228,10 +2228,10 @@
         <v>87</v>
       </c>
       <c r="CX2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="CY2">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="CZ2">
         <v>67</v>
@@ -2252,28 +2252,28 @@
         <v>83</v>
       </c>
       <c r="DF2">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="DG2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="DH2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="DI2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="DJ2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="DK2">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="DL2">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="DM2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="DN2">
         <v>53</v>
@@ -2282,22 +2282,22 @@
         <v>66</v>
       </c>
       <c r="DP2">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="DQ2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="DR2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="DS2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="DT2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="DU2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="DV2">
         <v>93</v>
@@ -2366,10 +2366,10 @@
         <v>33</v>
       </c>
       <c r="ER2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="ES2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="ET2">
         <v>29</v>
@@ -2384,16 +2384,16 @@
         <v>60</v>
       </c>
       <c r="EX2">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="EY2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="EZ2">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="FA2">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="FB2">
         <v>33</v>
@@ -2402,10 +2402,10 @@
         <v>49</v>
       </c>
       <c r="FD2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="FE2">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="FF2">
         <v>45</v>
@@ -2456,16 +2456,16 @@
         <v>110</v>
       </c>
       <c r="FV2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="FW2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="FX2">
         <v>44</v>
       </c>
       <c r="FY2">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="FZ2">
         <v>6</v>
@@ -2528,10 +2528,10 @@
         <v>33</v>
       </c>
       <c r="GT2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="GU2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="GV2">
         <v>46</v>
@@ -2564,10 +2564,10 @@
         <v>123</v>
       </c>
       <c r="HF2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="HG2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="HH2">
         <v>68</v>
@@ -2576,10 +2576,10 @@
         <v>74</v>
       </c>
       <c r="HJ2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="HK2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="HL2">
         <v>51</v>
@@ -2588,16 +2588,16 @@
         <v>68</v>
       </c>
       <c r="HN2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="HO2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="HP2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="HQ2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="HR2">
         <v>62</v>
@@ -2612,16 +2612,16 @@
         <v>72</v>
       </c>
       <c r="HV2">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="HW2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="HX2">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="HY2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="HZ2">
         <v>108</v>
@@ -2636,10 +2636,10 @@
         <v>108</v>
       </c>
       <c r="ID2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="IE2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="IF2">
         <v>102</v>
@@ -2690,16 +2690,16 @@
         <v>107</v>
       </c>
       <c r="IV2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="IW2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="IX2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="IY2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="IZ2">
         <v>119</v>
@@ -2720,16 +2720,16 @@
         <v>83</v>
       </c>
       <c r="JF2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="JG2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="JH2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="JI2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="JJ2">
         <v>173</v>
@@ -2750,40 +2750,40 @@
         <v>252</v>
       </c>
       <c r="JP2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="JQ2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="JR2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="JS2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="JT2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="JU2">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="JV2">
         <v>42</v>
       </c>
       <c r="JW2">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="JX2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="JY2">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="JZ2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="KA2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="KB2">
         <v>93</v>
@@ -2840,16 +2840,16 @@
         <v>162</v>
       </c>
       <c r="KT2">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="KU2">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="KV2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="KW2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="KX2">
         <v>90</v>
